--- a/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEHC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>GEHC</t>
   </si>
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5295000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5131000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5698000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5143000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5007000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4777000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5319000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4863000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4839000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4650000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5206000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4822000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4817000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4707000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4938000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4576000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4484000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4343000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4589000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8692000</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3115000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3154000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3437000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3154000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3023000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2765000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3044000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2838000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2837000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2749000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3050000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2887000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2877000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2816000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3006000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2803000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2688000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2665000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2727000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5146000</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2180000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1977000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2261000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1989000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1984000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2012000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2275000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2025000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2002000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1901000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2156000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1935000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1940000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1891000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1932000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1773000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1796000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1678000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1862000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3546000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,76 +1001,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>323000</v>
+      </c>
+      <c r="E12" s="3">
         <v>345000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>323000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>292000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>302000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>344000</v>
       </c>
       <c r="I12" s="3">
         <v>344000</v>
       </c>
       <c r="J12" s="3">
+        <v>344000</v>
+      </c>
+      <c r="K12" s="3">
         <v>316000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>327000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>324000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>315000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>322000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>298000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>270000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>271000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>260000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>257000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>238000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>225000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>391000</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,52 +1141,55 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-96000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-17000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1192,53 +1212,56 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E15" s="3">
         <v>153000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>146000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>148000</v>
       </c>
       <c r="G15" s="3">
         <v>148000</v>
       </c>
       <c r="H15" s="3">
+        <v>148000</v>
+      </c>
+      <c r="I15" s="3">
         <v>136000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>140000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>143000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>149000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>148000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>144000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>153000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>156000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>157000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4502000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4562000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4802000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4412000</v>
       </c>
-      <c r="G17" s="3">
-        <v>4275000</v>
-      </c>
       <c r="H17" s="3">
+        <v>4280000</v>
+      </c>
+      <c r="I17" s="3">
         <v>4071000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4414000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4082000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4126000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4006000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4498000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4087000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4125000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4031000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4161000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3971000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3853000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3834000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3862000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7276000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>793000</v>
+      </c>
+      <c r="E18" s="3">
         <v>569000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>896000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>731000</v>
       </c>
-      <c r="G18" s="3">
-        <v>732000</v>
-      </c>
       <c r="H18" s="3">
+        <v>727000</v>
+      </c>
+      <c r="I18" s="3">
         <v>706000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>905000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>781000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>713000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>644000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>708000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>735000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>692000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>676000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>777000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>605000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>631000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>509000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>727000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1416000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,348 +1478,364 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-51000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>93000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-28000</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-12000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>33000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-12000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-16000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>38000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-25000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-23000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>19000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>20000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>28000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>34000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>52000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>979000</v>
+      </c>
+      <c r="E21" s="3">
         <v>773000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>949000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>907000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>880000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>854000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1012000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>936000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>868000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>808000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>814000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>913000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>871000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>835000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>934000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>784000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>808000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>696000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>915000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1784000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E22" s="3">
         <v>115000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>128000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>124000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>122000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>37000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>141000</v>
       </c>
       <c r="K22" s="3">
         <v>141000</v>
       </c>
       <c r="L22" s="3">
+        <v>141000</v>
+      </c>
+      <c r="M22" s="3">
         <v>148000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>68000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>147000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>145000</v>
       </c>
       <c r="P22" s="3">
         <v>145000</v>
       </c>
       <c r="Q22" s="3">
+        <v>145000</v>
+      </c>
+      <c r="R22" s="3">
         <v>59000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>24000</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>693000</v>
+      </c>
+      <c r="E23" s="3">
         <v>505000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>821000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>643000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>613000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>692000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>834000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>657000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>578000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>512000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>609000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>636000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>570000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>546000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>718000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>622000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>639000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>533000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>755000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1444000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E24" s="3">
         <v>94000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>219000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>179000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>113000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>104000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>96000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>168000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>143000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>124000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>193000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>250000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>137000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>163000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>151000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>128000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>153000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>131000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>179000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>261000</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>574000</v>
+      </c>
+      <c r="E26" s="3">
         <v>411000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>602000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>464000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>500000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>588000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>738000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>489000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>435000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>388000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>416000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>386000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>433000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>383000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>567000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>494000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>486000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>402000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>576000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1183000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E27" s="3">
         <v>389000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>589000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>446000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>486000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>564000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>721000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>470000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>428000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>374000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>403000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>375000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>418000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>189000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>548000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>488000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>473000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>389000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>564000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1162000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2093,40 +2154,43 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-4000</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>6000</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>12000</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>7000</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E32" s="3">
         <v>51000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-93000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>28000</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I32" s="3">
         <v>12000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-33000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>12000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>16000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-38000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>25000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>23000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-19000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-20000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-28000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-34000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-52000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E33" s="3">
         <v>389000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>589000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>446000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>486000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>564000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>721000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>470000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>428000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>374000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>403000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>375000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>418000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>189000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>554000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>488000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>485000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>389000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>564000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1169000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E35" s="3">
         <v>389000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>589000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>446000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>486000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>564000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>721000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>470000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>428000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>374000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>403000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>375000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>418000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>189000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>554000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>488000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>485000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>389000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>564000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1169000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,62 +2744,63 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2079000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2261000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4492000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4005000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3737000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2454000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2873000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3550000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1998000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2551000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2494000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2408000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1936000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2324000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1445000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>500000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>525000</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,8 +2813,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,62 +2884,65 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4913000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4739000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4849000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4681000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4475000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4350000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4360000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4203000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4057000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4017000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4307000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4147000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4140000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4097000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4301000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3990000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4141000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2862,62 +2955,65 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2483000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2353000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2234000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2304000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2283000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2158000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1939000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2124000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2023000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1989000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1960000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2128000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2264000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2256000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2155000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2200000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2237000</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,62 +3026,65 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>695000</v>
+      </c>
+      <c r="E45" s="3">
         <v>729000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>679000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>646000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>550000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>505000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>525000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>547000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>493000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>559000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>492000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>775000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>897000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>924000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>417000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>588000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>505000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,62 +3097,65 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10497000</v>
+      </c>
+      <c r="E46" s="3">
         <v>10426000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12501000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11893000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11308000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9735000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9901000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10638000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8806000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9373000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9410000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9468000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9240000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9604000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8318000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7278000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7408000</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3066,52 +3168,55 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E47" s="3">
         <v>352000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>351000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>302000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>244000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>235000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>373000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>361000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>340000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>346000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>357000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3134,62 +3239,65 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3146000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3095000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3092000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3010000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2962000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2851000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2550000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2539000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2458000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2445000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2500000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2355000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2357000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2327000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2314000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2080000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2161000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3202,62 +3310,65 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16989000</v>
+      </c>
+      <c r="E49" s="3">
         <v>16968000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14619000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14604000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14637000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14611000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14214000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14270000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14311000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14101000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14189000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14246000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14352000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14418000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14333000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14365000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14520000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,62 +3523,65 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1265000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1277000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1251000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1281000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1292000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1180000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1102000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1371000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1223000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1174000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1178000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1662000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1643000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1596000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2574000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2344000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2375000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,62 +3665,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37246000</v>
+      </c>
+      <c r="E54" s="3">
         <v>37125000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36906000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36127000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35500000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33586000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33089000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33855000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31852000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32208000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32454000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32382000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32311000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32637000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27539000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26067000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26464000</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,62 +3792,63 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3231000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3410000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3250000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2987000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2975000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3152000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3035000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2911000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2824000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2931000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2947000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2774000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2835000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2977000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2944000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2687000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2702000</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3730,62 +3861,65 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E58" s="3">
         <v>139000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>642000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2139000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2132000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2121000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1617000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1121000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1120000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1117000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1116000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>5000</v>
       </c>
       <c r="P58" s="3">
         <v>5000</v>
       </c>
       <c r="Q58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="R58" s="3">
         <v>15000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,62 +3932,65 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2955000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2998000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2983000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2812000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2767000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2820000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2866000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2691000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2707000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2798000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2932000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4784000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4741000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5254000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4232000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3936000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3985000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,62 +4003,65 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8302000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8529000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9105000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10073000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9748000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9969000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9553000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8670000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8318000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8859000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8981000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7565000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7581000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8236000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7191000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6635000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6693000</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,62 +4074,65 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10408000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10438000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9821000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8605000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8584000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7063000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7759000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9612000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8542000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8551000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8747000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10618000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10603000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10575000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8234000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>30000</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4002,62 +4145,65 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>960000</v>
+      </c>
+      <c r="E62" s="3">
         <v>885000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>932000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>996000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>950000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>810000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>800000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>910000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>802000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>818000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>861000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>778000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>886000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>843000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2522000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2325000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2467000</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,62 +4429,65 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26028000</v>
+      </c>
+      <c r="E66" s="3">
         <v>26227000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26307000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25907000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25547000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24168000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24437000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25343000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23858000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24609000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25144000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25079000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24988000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25740000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18182000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9208000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9433000</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,62 +4811,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6199000</v>
+      </c>
+      <c r="E72" s="3">
         <v>5654000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5281000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4709000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4295000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3810000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3262000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2558000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2101000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1687000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1326000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>937000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>576000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>185000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11235000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18801000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18680000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,62 +5095,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10975000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10668000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10379000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9993000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9712000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9187000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8446000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8317000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7801000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7408000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7133000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7131000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7102000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6690000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9357000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16859000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17031000</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E81" s="3">
         <v>389000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>589000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>446000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>486000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>564000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>721000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>470000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>428000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>374000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>403000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>375000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>418000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>189000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>554000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>488000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>485000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>389000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>564000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1169000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5413,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E83" s="3">
         <v>66000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>65000</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>69000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>68000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>60000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>64000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>63000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>61000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>59000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>57000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>56000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>157000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>160000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>157000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>159000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>154000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>316000</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E89" s="3">
         <v>290000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1050000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>593000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>94000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>250000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>913000</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>-119000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>419000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1050000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>650000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-67000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>468000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1042000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>622000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-19000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>468000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-11000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1040000</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-178000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-134000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-110000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-86000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-152000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-102000</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3">
         <v>-64000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-145000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-94000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-80000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-70000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-143000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-77000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-74000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-59000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-73000</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-115000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2500000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-269000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-148000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-223000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-407000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-240000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-349000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-188000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-88000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-120000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-84000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-266000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-95000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-118000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-85000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1532000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-145000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6036,31 +6270,31 @@
         <v>16000</v>
       </c>
       <c r="I96" s="3">
+        <v>16000</v>
+      </c>
+      <c r="J96" s="3">
         <v>14000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K96" s="3">
-        <v>14000</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>14000</v>
       </c>
       <c r="M96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="N96" s="3">
         <v>13000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>14000</v>
       </c>
       <c r="O96" s="3">
         <v>14000</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,208 +6530,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-236000</v>
+      </c>
+      <c r="E100" s="3">
         <v>21000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-292000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-165000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1361000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-286000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1276000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>-57000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-153000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-900000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-24000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-227000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>673000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-37000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-505000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>140000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-420000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1401000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1079000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E101" s="3">
         <v>27000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-75000</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3">
         <v>-22000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-19000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>24000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-31000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>37000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-25000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>37000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-25000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-12000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-11000</v>
       </c>
       <c r="V101" s="3">
         <v>-11000</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3">
+        <v>-11000</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-181000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2226000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>487000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>264000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1289000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-416000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-678000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-547000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>59000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>86000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>475000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-389000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>883000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>947000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-26000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>24000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-55000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-153000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-195000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
